--- a/education_forms/035_education_impact_transformation_grant_application_form--education_forms.xlsx
+++ b/education_forms/035_education_impact_transformation_grant_application_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>What is the applicant's name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is the applicant's email address?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What is the applicant's phone number?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>What category does the applicant fall under?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>What is the applicant's address?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>What is the application date?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>What is the application time?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Are there any additional notes that the applicant would like to add?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>What are the required fields that need to be filled?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,358 +732,197 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What are the email options?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>required_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>What are the phone options?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>required_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What are the category options?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>required_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What are the address options?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>required_6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>What are the select multiple options for name?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>required_7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>What are the select multiple options for email?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>required_8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>What are the select multiple options for phone?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>required_9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>What are the select multiple options for category?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>required_10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>What are the select multiple options for address?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>required_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>required_2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>required_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>required_1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'education_forms',_'label':_'education_forms'}</t>
+          <t>education_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Education Forms', 'label': 'Education Forms'}</t>
+          <t>Education Forms</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'scholarship_application_forms',_'label':_'scholarship_application_forms'}</t>
+          <t>scholarship_application_forms</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Scholarship Application Forms', 'label': 'Scholarship Application Forms'}</t>
+          <t>Scholarship Application Forms</t>
         </is>
       </c>
     </row>
@@ -1165,352 +1004,624 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other_forms',_'label':_'other_forms'}</t>
+          <t>other_forms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other Forms', 'label': 'Other Forms'}</t>
+          <t>Other Forms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>required_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>email_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'label': 'option 1', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>email 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>required_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'label': 'option 2', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>email 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>required_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'label':_'option_3',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>email_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option_3', 'label': 'option 3', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>email 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>required_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'option_4',_'label':_'option_4',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>email_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'option_4', 'label': 'option 4', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>email 4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>email_choices</t>
+          <t>required_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email_1',_'label':_'email_1',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>phone_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'email_1', 'label': 'email_1', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>phone 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>email_choices</t>
+          <t>required_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email_2',_'label':_'email_2',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'email_2', 'label': 'email_2', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>phone 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>email_choices</t>
+          <t>required_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'email_3',_'label':_'email_3',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>phone_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'email_3', 'label': 'email_3', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>phone 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>email_choices</t>
+          <t>required_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'email_4',_'label':_'email_4',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>phone_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'email_4', 'label': 'email_4', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>phone 4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>phone_choices</t>
+          <t>required_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone_1',_'label':_'phone_1',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'phone_1', 'label': 'phone_1', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>phone_choices</t>
+          <t>required_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone_2',_'label':_'phone_2',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'phone_2', 'label': 'phone_2', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>phone_choices</t>
+          <t>required_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'phone_3',_'label':_'phone_3',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'phone_3', 'label': 'phone_3', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>phone_choices</t>
+          <t>required_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'phone_4',_'label':_'phone_4',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'phone_4', 'label': 'phone_4', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>required_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>address_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'label': 'option 1', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>address 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>required_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'label': 'option 2', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>address 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>required_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'label':_'option_3',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>address_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option_3', 'label': 'option 3', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>address 3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>required_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'option_4',_'label':_'option_4',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>address_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'option_4', 'label': 'option 4', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>address 4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>address_choices</t>
+          <t>required_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'address_1',_'label':_'address_1',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'address_1', 'label': 'address_1', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>address_choices</t>
+          <t>required_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'address_2',_'label':_'address_2',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'address_2', 'label': 'address_2', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>address_choices</t>
+          <t>required_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'address_3',_'label':_'address_3',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'address_3', 'label': 'address_3', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>address_choices</t>
+          <t>required_6_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'address_4',_'label':_'address_4',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'address_4', 'label': 'address_4', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>required_7_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>email_1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>email 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>required_7_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>email_2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>email 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>required_7_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>email_3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>email 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>required_7_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>email_4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>email 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>required_8_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>phone_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>phone 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>required_8_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>phone_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>phone 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>required_8_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>phone_3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>phone 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>required_8_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>phone_4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>phone 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>required_9_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>required_9_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>required_9_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>required_9_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>required_10_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>address_1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>address 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>required_10_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>address_2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>address 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>required_10_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>address_3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>address 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>required_10_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>address_4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>address 4</t>
         </is>
       </c>
     </row>
